--- a/s11.xlsx
+++ b/s11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27E4A806-246A-4D65-8726-BB2EB5931C2D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1ECF41-92A1-469A-A8DC-755C5998718B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8520" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="星动" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="129">
   <si>
     <t>歌名</t>
   </si>
@@ -485,6 +485,35 @@
     <t>B：中间滑点后,立马压爆第一个左单点
 E：左滑点第二个</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>影子</t>
+  </si>
+  <si>
+    <t>A Sky Full Of Stars</t>
+  </si>
+  <si>
+    <t>身边</t>
+  </si>
+  <si>
+    <t>硬糖</t>
+  </si>
+  <si>
+    <t>Kidult</t>
+  </si>
+  <si>
+    <t>Gamble Rumble</t>
+  </si>
+  <si>
+    <t>身边</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬糖</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>请站在左边等我</t>
   </si>
 </sst>
 </file>
@@ -492,7 +521,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0_ "/>
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -617,7 +646,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -678,13 +707,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -711,26 +737,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1039,18 +1050,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="38.125" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="24" customWidth="1"/>
+    <col min="1" max="1" width="38.125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="23" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
     <col min="4" max="4" width="28.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="9" style="3"/>
     <col min="6" max="6" width="25.375" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="9.625" customWidth="1"/>
-    <col min="9" max="9" width="13.25" style="26" customWidth="1"/>
+    <col min="9" max="9" width="13.25" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="22.5" x14ac:dyDescent="0.15">
@@ -1092,67 +1103,115 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="23">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A14" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A15" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1164,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -1194,93 +1253,141 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>6</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="26"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="23">
         <v>6</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="26"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <v>6</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="26"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="23">
         <v>7</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="26"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="26"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="26"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>8</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="26"/>
+      <c r="E8" s="25"/>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>8</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A14" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A15" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -1290,10 +1397,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="35" style="28" customWidth="1"/>
+    <col min="1" max="1" width="35" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="22.5" x14ac:dyDescent="0.15">
@@ -1335,67 +1442,115 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="23">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1407,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -1437,103 +1592,152 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>6</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="26"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="23">
         <v>6</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="26"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <v>6</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="26"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="23">
         <v>7</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="26"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="26"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="26"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>8</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="26"/>
+      <c r="E8" s="25"/>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>8</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="23">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="34.625" customWidth="1"/>
@@ -1598,7 +1802,7 @@
       <c r="D2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="30" t="s">
         <v>114</v>
       </c>
       <c r="F2" s="10" t="s">
@@ -1607,7 +1811,7 @@
       <c r="G2" s="9">
         <v>59.5</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="30" t="s">
         <v>114</v>
       </c>
       <c r="I2" s="11" t="s">
@@ -1636,16 +1840,16 @@
       <c r="D3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="28" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="9">
         <v>64.2</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="30" t="s">
         <v>110</v>
       </c>
       <c r="I3" s="12" t="s">
@@ -1706,13 +1910,13 @@
       <c r="B5" s="8">
         <v>7</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>117</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="30" t="s">
         <v>116</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -1788,7 +1992,7 @@
       <c r="D7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="30" t="s">
         <v>109</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -1823,13 +2027,13 @@
       <c r="C8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="28" t="s">
         <v>118</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>119</v>
       </c>
       <c r="G8" s="9">
@@ -1849,6 +2053,46 @@
       </c>
       <c r="L8" s="9">
         <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +2104,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -1892,15 +2136,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>6</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="25"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
@@ -1978,10 +2222,10 @@
       <c r="B6" s="8">
         <v>7</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="28" t="s">
         <v>112</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -2004,7 +2248,7 @@
       <c r="C7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="28" t="s">
         <v>115</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -2062,6 +2306,71 @@
       <c r="G9" s="9">
         <v>510</v>
       </c>
+    </row>
+    <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="7">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="7">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="7">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="7">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -2074,7 +2383,7 @@
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="1" max="1" width="28.875" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="7.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="31.5" customWidth="1"/>
@@ -2142,7 +2451,7 @@
       <c r="E2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="28" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="9">
@@ -2184,16 +2493,16 @@
       <c r="A4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="8">
-        <v>6</v>
-      </c>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="17">
+        <v>6</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>107</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="32" t="s">
         <v>108</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -2202,7 +2511,7 @@
       <c r="G4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="18" t="s">
         <v>65</v>
       </c>
       <c r="I4" s="11" t="s">
@@ -2222,31 +2531,31 @@
       <c r="A5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8">
-        <v>7</v>
-      </c>
-      <c r="C5" s="34" t="s">
+      <c r="B5" s="17">
+        <v>7</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="18">
         <v>55.7</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="28" t="s">
         <v>99</v>
       </c>
       <c r="K5" s="9">
@@ -2260,25 +2569,25 @@
       <c r="A6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="17">
         <v>8</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="18" t="s">
         <v>69</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="18">
         <v>57.4</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="18" t="s">
         <v>67</v>
       </c>
       <c r="I6" s="11" t="s">
@@ -2298,25 +2607,25 @@
       <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="17">
         <v>8</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="18" t="s">
         <v>72</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="18">
         <v>53.7</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="31" t="s">
         <v>106</v>
       </c>
       <c r="I7" s="11" t="s">
@@ -2339,31 +2648,31 @@
       <c r="B8" s="17">
         <v>8</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="28" t="s">
         <v>103</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>104</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="31" t="s">
         <v>97</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="21">
         <v>25</v>
       </c>
       <c r="L8" s="18">
@@ -2380,7 +2689,7 @@
       <c r="C9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="28" t="s">
         <v>96</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -2408,33 +2717,131 @@
         <v>308</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D10" s="19"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D11" s="19"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D12" s="19"/>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D13" s="19"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D14" s="19"/>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D15" s="19"/>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="D16" s="19"/>
-      <c r="E16" s="3"/>
+    <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="15">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="15">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="15">
+        <v>7</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="15">
+        <v>7</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A14" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="15">
+        <v>7</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="15">
+        <v>9</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+      <c r="A16" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="15">
+        <v>9</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="19"/>
@@ -2505,7 +2912,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -2651,7 +3058,7 @@
       <c r="C7" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="28" t="s">
         <v>95</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -2709,6 +3116,69 @@
       <c r="G9" s="9">
         <v>308</v>
       </c>
+    </row>
+    <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="7">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="7">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="7">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="7">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="7">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="7">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="7">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/s11.xlsx
+++ b/s11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1ECF41-92A1-469A-A8DC-755C5998718B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1C5751-B003-4052-8647-63AF605F2FA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="星动" sheetId="1" r:id="rId1"/>
@@ -217,10 +217,6 @@
 E：右单点(本曲结束)</t>
   </si>
   <si>
-    <t>A：左边滑条结束，立马爆左点+右滑点
-E：右边单点</t>
-  </si>
-  <si>
     <t>A12</t>
   </si>
   <si>
@@ -514,6 +510,11 @@
   </si>
   <si>
     <t>请站在左边等我</t>
+  </si>
+  <si>
+    <t>A：左边滑条结束，立马爆左点+右滑点
+E：右边单点</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1168,7 +1169,7 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A10" s="27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1176,7 +1177,7 @@
     </row>
     <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A11" s="27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -1184,7 +1185,7 @@
     </row>
     <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A12" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1192,7 +1193,7 @@
     </row>
     <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A13" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1200,7 +1201,7 @@
     </row>
     <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A14" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1208,7 +1209,7 @@
     </row>
     <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A15" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -1343,7 +1344,7 @@
     </row>
     <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A10" s="27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1351,7 +1352,7 @@
     </row>
     <row r="11" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A11" s="27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -1359,7 +1360,7 @@
     </row>
     <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A12" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1367,7 +1368,7 @@
     </row>
     <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A13" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1375,7 +1376,7 @@
     </row>
     <row r="14" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A14" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1383,7 +1384,7 @@
     </row>
     <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A15" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -1507,7 +1508,7 @@
     </row>
     <row r="10" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="23">
         <v>6</v>
@@ -1515,7 +1516,7 @@
     </row>
     <row r="11" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="23">
         <v>6</v>
@@ -1523,7 +1524,7 @@
     </row>
     <row r="12" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="23">
         <v>7</v>
@@ -1531,7 +1532,7 @@
     </row>
     <row r="13" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13" s="23">
         <v>7</v>
@@ -1539,7 +1540,7 @@
     </row>
     <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="23">
         <v>9</v>
@@ -1547,7 +1548,7 @@
     </row>
     <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" s="23">
         <v>9</v>
@@ -1682,7 +1683,7 @@
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="23">
         <v>6</v>
@@ -1690,7 +1691,7 @@
     </row>
     <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="23">
         <v>6</v>
@@ -1698,7 +1699,7 @@
     </row>
     <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="23">
         <v>7</v>
@@ -1706,7 +1707,7 @@
     </row>
     <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13" s="23">
         <v>7</v>
@@ -1714,7 +1715,7 @@
     </row>
     <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="23">
         <v>9</v>
@@ -1722,7 +1723,7 @@
     </row>
     <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" s="23">
         <v>9</v>
@@ -1803,7 +1804,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>26</v>
@@ -1812,7 +1813,7 @@
         <v>59.5</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>27</v>
@@ -1841,16 +1842,16 @@
         <v>29</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G3" s="9">
         <v>64.2</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>31</v>
@@ -1911,13 +1912,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>37</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>38</v>
@@ -1993,7 +1994,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>45</v>
@@ -2028,13 +2029,13 @@
         <v>46</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" s="9">
         <v>58.9</v>
@@ -2057,7 +2058,7 @@
     </row>
     <row r="9" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9" s="7">
         <v>6</v>
@@ -2065,7 +2066,7 @@
     </row>
     <row r="10" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="7">
         <v>6</v>
@@ -2073,7 +2074,7 @@
     </row>
     <row r="11" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11" s="7">
         <v>7</v>
@@ -2081,7 +2082,7 @@
     </row>
     <row r="12" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" s="7">
         <v>8</v>
@@ -2089,7 +2090,7 @@
     </row>
     <row r="13" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" s="7">
         <v>10</v>
@@ -2126,13 +2127,13 @@
         <v>9</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27" x14ac:dyDescent="0.15">
@@ -2144,7 +2145,7 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
@@ -2159,14 +2160,14 @@
       <c r="D3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="9">
+        <v>56.7</v>
+      </c>
+      <c r="F3" s="9">
+        <v>305</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F3" s="9">
-        <v>56.7</v>
-      </c>
-      <c r="G3" s="9">
-        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -2182,14 +2183,14 @@
       <c r="D4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="9">
+        <v>57</v>
+      </c>
+      <c r="F4" s="9">
+        <v>271</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F4" s="9">
-        <v>57</v>
-      </c>
-      <c r="G4" s="9">
-        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -2205,14 +2206,14 @@
       <c r="D5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="9">
+        <v>58.1</v>
+      </c>
+      <c r="F5" s="9">
+        <v>379</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" s="9">
-        <v>58.1</v>
-      </c>
-      <c r="G5" s="9">
-        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
@@ -2223,19 +2224,19 @@
         <v>7</v>
       </c>
       <c r="C6" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="9">
+        <v>61.2</v>
+      </c>
+      <c r="F6" s="9">
+        <v>242</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="9">
-        <v>61.2</v>
-      </c>
-      <c r="G6" s="9">
-        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -2249,16 +2250,16 @@
         <v>54</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="9">
+        <v>62.9</v>
+      </c>
+      <c r="F7" s="9">
+        <v>391</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" s="9">
-        <v>62.9</v>
-      </c>
-      <c r="G7" s="9">
-        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
@@ -2274,14 +2275,14 @@
       <c r="D8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="9">
+        <v>63.8</v>
+      </c>
+      <c r="F8" s="9">
+        <v>409</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" s="9">
-        <v>63.8</v>
-      </c>
-      <c r="G8" s="9">
-        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
@@ -2294,22 +2295,22 @@
       <c r="C9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="9">
+        <v>67.2</v>
+      </c>
+      <c r="F9" s="9">
+        <v>510</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="F9" s="9">
-        <v>67.2</v>
-      </c>
-      <c r="G9" s="9">
-        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" s="7">
         <v>6</v>
@@ -2322,7 +2323,7 @@
     </row>
     <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" s="7">
         <v>6</v>
@@ -2335,7 +2336,7 @@
     </row>
     <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="7">
         <v>7</v>
@@ -2348,7 +2349,7 @@
     </row>
     <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13" s="7">
         <v>8</v>
@@ -2361,7 +2362,7 @@
     </row>
     <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="7">
         <v>10</v>
@@ -2375,6 +2376,7 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2383,8 +2385,8 @@
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="28.875" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="28.875" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="31.5" customWidth="1"/>
     <col min="5" max="5" width="7.25" customWidth="1"/>
@@ -2398,11 +2400,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
@@ -2436,35 +2438,35 @@
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="8">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8">
-        <v>6</v>
-      </c>
       <c r="C2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="F2" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="9">
         <v>51.6</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>31</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K2" s="9">
         <v>27.5</v>
@@ -2474,11 +2476,11 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="8">
+        <v>6</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="8">
-        <v>6</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -2490,35 +2492,35 @@
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17">
+        <v>6</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="17">
-        <v>6</v>
-      </c>
       <c r="C4" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>65</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>31</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K4" s="9">
         <v>30.4</v>
@@ -2528,35 +2530,35 @@
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="17">
+        <v>7</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="17">
-        <v>7</v>
-      </c>
       <c r="C5" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="E5" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="28" t="s">
         <v>99</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="G5" s="18">
         <v>55.7</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K5" s="9">
         <v>27.8</v>
@@ -2566,35 +2568,35 @@
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17">
+        <v>8</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="17">
-        <v>8</v>
-      </c>
       <c r="C6" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="G6" s="18">
         <v>57.4</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6" s="9">
         <v>28.7</v>
@@ -2604,35 +2606,35 @@
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="17">
+        <v>8</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="17">
-        <v>8</v>
-      </c>
       <c r="C7" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="G7" s="18">
         <v>53.7</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K7" s="9">
         <v>27.3</v>
@@ -2642,35 +2644,35 @@
       </c>
     </row>
     <row r="8" spans="1:12" s="14" customFormat="1" ht="54" x14ac:dyDescent="0.15">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17">
+        <v>8</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17">
-        <v>8</v>
-      </c>
       <c r="C8" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="H8" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>27</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K8" s="21">
         <v>25</v>
@@ -2680,35 +2682,35 @@
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="8">
+        <v>9</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="8">
-        <v>9</v>
-      </c>
       <c r="C9" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G9" s="9">
         <v>54.7</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K9" s="9">
         <v>27.8</v>
@@ -2718,11 +2720,11 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="15">
-        <v>6</v>
+      <c r="A10" s="15">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -2736,11 +2738,11 @@
       <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A11" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="15">
-        <v>6</v>
+      <c r="A11" s="15">
+        <v>6</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -2754,11 +2756,11 @@
       <c r="L11" s="15"/>
     </row>
     <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="15">
-        <v>7</v>
+      <c r="A12" s="15">
+        <v>7</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -2772,11 +2774,11 @@
       <c r="L12" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="15">
-        <v>7</v>
+      <c r="A13" s="15">
+        <v>7</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>122</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -2790,11 +2792,11 @@
       <c r="L13" s="15"/>
     </row>
     <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A14" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="15">
-        <v>7</v>
+      <c r="A14" s="15">
+        <v>7</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -2808,11 +2810,11 @@
       <c r="L14" s="15"/>
     </row>
     <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A15" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="15">
         <v>9</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -2826,11 +2828,11 @@
       <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A16" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="15">
         <v>9</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>124</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
@@ -2934,13 +2936,13 @@
         <v>9</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -2951,19 +2953,19 @@
         <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9">
+        <v>47.9</v>
+      </c>
+      <c r="F2" s="9">
+        <v>135</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F2" s="9">
-        <v>47.9</v>
-      </c>
-      <c r="G2" s="9">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -2975,9 +2977,9 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="12"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
@@ -2987,19 +2989,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9">
+        <v>53.4</v>
+      </c>
+      <c r="F4" s="9">
+        <v>143</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F4" s="9">
-        <v>53.4</v>
-      </c>
-      <c r="G4" s="9">
-        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -3010,19 +3012,19 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9">
+        <v>54.8</v>
+      </c>
+      <c r="F5" s="9">
+        <v>214</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" s="9">
-        <v>54.8</v>
-      </c>
-      <c r="G5" s="9">
-        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -3033,19 +3035,19 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9">
+        <v>53.6</v>
+      </c>
+      <c r="F6" s="9">
+        <v>140</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="9">
-        <v>53.6</v>
-      </c>
-      <c r="G6" s="9">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -3056,19 +3058,19 @@
         <v>8</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="9">
+        <v>51.1</v>
+      </c>
+      <c r="F7" s="9">
+        <v>183</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" s="9">
-        <v>51.1</v>
-      </c>
-      <c r="G7" s="9">
-        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -3079,19 +3081,19 @@
         <v>8</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9">
+        <v>47.7</v>
+      </c>
+      <c r="F8" s="9">
+        <v>212</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" s="9">
-        <v>47.7</v>
-      </c>
-      <c r="G8" s="9">
-        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
@@ -3102,24 +3104,24 @@
         <v>8</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9">
+        <v>50.4</v>
+      </c>
+      <c r="F9" s="9">
+        <v>308</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F9" s="9">
-        <v>50.4</v>
-      </c>
-      <c r="G9" s="9">
-        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="7">
         <v>6</v>
@@ -3128,7 +3130,7 @@
     </row>
     <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="7">
         <v>6</v>
@@ -3137,7 +3139,7 @@
     </row>
     <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12" s="7">
         <v>7</v>
@@ -3146,7 +3148,7 @@
     </row>
     <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13" s="7">
         <v>7</v>
@@ -3155,7 +3157,7 @@
     </row>
     <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14" s="7">
         <v>7</v>
@@ -3164,7 +3166,7 @@
     </row>
     <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" s="7">
         <v>9</v>
@@ -3173,7 +3175,7 @@
     </row>
     <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" s="7">
         <v>9</v>
